--- a/examples/report/report.xlsx
+++ b/examples/report/report.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Чаще всего звонки теряются на этапе «Выявление потребности (открытые вопросы)» — 1 из 5.</t>
+          <t>Звонки теряются поровну на этапах «Выявление потребности (открытые вопросы)», «Отработка возражения» и «Следующий шаг» — по 1 из 5.</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>16.10.2026 12:05</t>
+          <t>16.10.2026 12:23</t>
         </is>
       </c>
     </row>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Возражение «Тишина, у нас рядом дорога.» без ответа по существу: в следующих 2 реплики менеджера нет фраз отработки («скидка», «рассрочка», «гарантия», «выгода»…).</t>
+          <t>Возражение «Ой, дороговато, я пока подумаю.» без ответа по существу: в следующих 2 реплики менеджера нет фраз отработки («скидка», «рассрочка», «гарантия», «выгода»…).</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>00:17 Клиент: «Тишина, у нас рядом дорога.»
-00:20 Менеджер: «Тогда я рекомендую двухкамерный пластиковый профиль, он хорошо глушит шум.»
-00:29 Менеджер: «Три окна выйдут примерно в 45 тысяч рублей.»</t>
+          <t>00:32 Клиент: «Ой, дороговато, я пока подумаю.»
+00:36 Менеджер: «Но, это наша цена, дешевле не получится.»
+00:43 Менеджер: «Хорошо, до свидания.»</t>
         </is>
       </c>
     </row>
